--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angelgalayodelacalle/Desktop/sabores-bot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0434CA-0D82-464B-A242-175F46822C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D0D70D-CB04-7C4C-A5C4-A3A1DCC4097F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15500" yWindow="1700" windowWidth="16820" windowHeight="17580" xr2:uid="{0A502601-D07A-A14C-90EB-855371072B55}"/>
   </bookViews>
@@ -386,60 +386,6 @@
     <t>Producto de La Chinata. Hecho con aceite de oliva.</t>
   </si>
   <si>
-    <t>Lip Gloss Hidratante Cereza</t>
-  </si>
-  <si>
-    <t>Bálsamo Reparador Labios y Nariz</t>
-  </si>
-  <si>
-    <t>Pack Bienvenida Natural Edition</t>
-  </si>
-  <si>
-    <t>Jabón Líquido</t>
-  </si>
-  <si>
-    <t>Crema Hidratante</t>
-  </si>
-  <si>
-    <t>Crema Hidronutritiva Facial 24h</t>
-  </si>
-  <si>
-    <t>Aceite Corporal</t>
-  </si>
-  <si>
-    <t>Acondicionador Capilar</t>
-  </si>
-  <si>
-    <t>Desodorante en Spray</t>
-  </si>
-  <si>
-    <t>Champú</t>
-  </si>
-  <si>
-    <t>Estuche Miniatura de Cosmética</t>
-  </si>
-  <si>
-    <t>Gel de Baño</t>
-  </si>
-  <si>
-    <t>Protector Labial SPF 15</t>
-  </si>
-  <si>
-    <t>Crema de Manos y Uñas</t>
-  </si>
-  <si>
-    <t>Jabón al Aceite de Oliva</t>
-  </si>
-  <si>
-    <t>Jabón Exfoliante</t>
-  </si>
-  <si>
-    <t>Jabón de Oliva Verde</t>
-  </si>
-  <si>
-    <t>Pack de Jabones de Oliva Mini</t>
-  </si>
-  <si>
     <t>Polen 100% natural.</t>
   </si>
   <si>
@@ -904,6 +850,60 @@
   </si>
   <si>
     <t>La Vera es una región conocida mundialmente por su Pimentón. El Pimentón de La Vera es característico por su sabor ahumado, el cual adquiere al ser secado con el humo de leña. El Pimentón dulce aporta a sus platos el delicioso sabor del Pimentón de La Vera. 70g.</t>
+  </si>
+  <si>
+    <t>Lip Gloss Hidratante Cereza La Chinata</t>
+  </si>
+  <si>
+    <t>Bálsamo Reparador Labios y Nariz La Chinata</t>
+  </si>
+  <si>
+    <t>Pack Bienvenida Natural Edition La Chinata</t>
+  </si>
+  <si>
+    <t>Crema Hidronutritiva Facial 24h La Chinata</t>
+  </si>
+  <si>
+    <t>Jabón Líquido La Chinata</t>
+  </si>
+  <si>
+    <t>Crema Hidratante La Chinata</t>
+  </si>
+  <si>
+    <t>Aceite Corporal La Chinata</t>
+  </si>
+  <si>
+    <t>Acondicionador Capilar La Chinata</t>
+  </si>
+  <si>
+    <t>Desodorante en Spray La Chinata</t>
+  </si>
+  <si>
+    <t>Champú La Chinata</t>
+  </si>
+  <si>
+    <t>Estuche Miniatura de Cosmética La Chinata</t>
+  </si>
+  <si>
+    <t>Gel de Baño La Chinata</t>
+  </si>
+  <si>
+    <t>Protector Labial SPF 15 La Chinata</t>
+  </si>
+  <si>
+    <t>Crema de Manos y Uñas La Chinata</t>
+  </si>
+  <si>
+    <t>Jabón al Aceite de Oliva La Chinata</t>
+  </si>
+  <si>
+    <t>Jabón Exfoliante La Chinata</t>
+  </si>
+  <si>
+    <t>Jabón de Oliva Verde La Chinata</t>
+  </si>
+  <si>
+    <t>Pack de Jabones de Oliva Mini La Chinata</t>
   </si>
 </sst>
 </file>
@@ -959,14 +959,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2034,7 +2033,7 @@
         <v>7.2</v>
       </c>
       <c r="D52" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
@@ -2048,7 +2047,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="D53" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
@@ -2062,7 +2061,7 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="D54" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
@@ -2076,7 +2075,7 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="D55" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
@@ -2090,7 +2089,7 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="D56" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
@@ -2104,7 +2103,7 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="D57" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
@@ -2118,7 +2117,7 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="D58" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -2132,7 +2131,7 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="D59" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
@@ -2146,7 +2145,7 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="D60" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
@@ -2160,12 +2159,12 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="D61" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="B62" t="s">
         <v>11</v>
@@ -2179,7 +2178,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B63" t="s">
         <v>11</v>
@@ -2188,12 +2187,12 @@
         <v>4.5</v>
       </c>
       <c r="D63" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="B64" t="s">
         <v>11</v>
@@ -2202,12 +2201,12 @@
         <v>89.9</v>
       </c>
       <c r="D64" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="B65" t="s">
         <v>11</v>
@@ -2216,12 +2215,12 @@
         <v>13.5</v>
       </c>
       <c r="D65" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B66" t="s">
         <v>11</v>
@@ -2230,12 +2229,12 @@
         <v>4.5</v>
       </c>
       <c r="D66" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="B67" t="s">
         <v>11</v>
@@ -2244,12 +2243,12 @@
         <v>4.5</v>
       </c>
       <c r="D67" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="B68" t="s">
         <v>11</v>
@@ -2258,12 +2257,12 @@
         <v>4.5</v>
       </c>
       <c r="D68" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="B69" t="s">
         <v>12</v>
@@ -2272,12 +2271,12 @@
         <v>2.8</v>
       </c>
       <c r="D69" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="B70" t="s">
         <v>12</v>
@@ -2286,12 +2285,12 @@
         <v>2.8</v>
       </c>
       <c r="D70" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="B71" t="s">
         <v>12</v>
@@ -2300,12 +2299,12 @@
         <v>2.8</v>
       </c>
       <c r="D71" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="B72" t="s">
         <v>12</v>
@@ -2314,12 +2313,12 @@
         <v>2.8</v>
       </c>
       <c r="D72" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="B73" t="s">
         <v>12</v>
@@ -2328,12 +2327,12 @@
         <v>2.8</v>
       </c>
       <c r="D73" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="B74" t="s">
         <v>12</v>
@@ -2342,12 +2341,12 @@
         <v>2.8</v>
       </c>
       <c r="D74" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="B75" t="s">
         <v>12</v>
@@ -2356,12 +2355,12 @@
         <v>3.3</v>
       </c>
       <c r="D75" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="B76" t="s">
         <v>12</v>
@@ -2370,12 +2369,12 @@
         <v>6.9</v>
       </c>
       <c r="D76" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="B77" t="s">
         <v>12</v>
@@ -2384,12 +2383,12 @@
         <v>6.9</v>
       </c>
       <c r="D77" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="B78" t="s">
         <v>12</v>
@@ -2398,12 +2397,12 @@
         <v>3.9</v>
       </c>
       <c r="D78" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="B79" t="s">
         <v>12</v>
@@ -2412,12 +2411,12 @@
         <v>3.9</v>
       </c>
       <c r="D79" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="B80" t="s">
         <v>12</v>
@@ -2426,12 +2425,12 @@
         <v>3.9</v>
       </c>
       <c r="D80" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -2440,7 +2439,7 @@
         <v>6.9</v>
       </c>
       <c r="D81" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
@@ -2454,7 +2453,7 @@
         <v>14.9</v>
       </c>
       <c r="D82" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
@@ -2468,12 +2467,12 @@
         <v>14.9</v>
       </c>
       <c r="D83" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -2482,12 +2481,12 @@
         <v>8.5</v>
       </c>
       <c r="D84" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -2496,26 +2495,26 @@
         <v>13.2</v>
       </c>
       <c r="D85" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="B86" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="C86">
         <v>16.399999999999999</v>
       </c>
       <c r="D86" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -2524,12 +2523,12 @@
         <v>5.8</v>
       </c>
       <c r="D87" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -2538,12 +2537,12 @@
         <v>13.3</v>
       </c>
       <c r="D88" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -2552,7 +2551,7 @@
         <v>19.899999999999999</v>
       </c>
       <c r="D89" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
@@ -2566,7 +2565,7 @@
         <v>20.9</v>
       </c>
       <c r="D90" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
@@ -2580,7 +2579,7 @@
         <v>11.9</v>
       </c>
       <c r="D91" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
@@ -2594,12 +2593,12 @@
         <v>11.9</v>
       </c>
       <c r="D92" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>116</v>
+        <v>249</v>
       </c>
       <c r="B93" t="s">
         <v>114</v>
@@ -2613,7 +2612,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>117</v>
+        <v>250</v>
       </c>
       <c r="B94" t="s">
         <v>114</v>
@@ -2627,7 +2626,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>118</v>
+        <v>251</v>
       </c>
       <c r="B95" t="s">
         <v>114</v>
@@ -2641,7 +2640,7 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>121</v>
+        <v>252</v>
       </c>
       <c r="B96" t="s">
         <v>114</v>
@@ -2655,7 +2654,7 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>119</v>
+        <v>253</v>
       </c>
       <c r="B97" t="s">
         <v>114</v>
@@ -2669,7 +2668,7 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>120</v>
+        <v>254</v>
       </c>
       <c r="B98" t="s">
         <v>114</v>
@@ -2683,7 +2682,7 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>122</v>
+        <v>255</v>
       </c>
       <c r="B99" t="s">
         <v>114</v>
@@ -2697,7 +2696,7 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>123</v>
+        <v>256</v>
       </c>
       <c r="B100" t="s">
         <v>114</v>
@@ -2711,7 +2710,7 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>124</v>
+        <v>257</v>
       </c>
       <c r="B101" t="s">
         <v>114</v>
@@ -2735,7 +2734,7 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>125</v>
+        <v>258</v>
       </c>
       <c r="B102" t="s">
         <v>114</v>
@@ -2749,7 +2748,7 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>126</v>
+        <v>259</v>
       </c>
       <c r="B103" t="s">
         <v>114</v>
@@ -2763,7 +2762,7 @@
     </row>
     <row r="104" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>127</v>
+        <v>260</v>
       </c>
       <c r="B104" t="s">
         <v>114</v>
@@ -2777,7 +2776,7 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>128</v>
+        <v>261</v>
       </c>
       <c r="B105" t="s">
         <v>114</v>
@@ -2791,7 +2790,7 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>129</v>
+        <v>262</v>
       </c>
       <c r="B106" t="s">
         <v>114</v>
@@ -2805,7 +2804,7 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>130</v>
+        <v>263</v>
       </c>
       <c r="B107" t="s">
         <v>114</v>
@@ -2819,7 +2818,7 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>131</v>
+        <v>264</v>
       </c>
       <c r="B108" t="s">
         <v>114</v>
@@ -2833,7 +2832,7 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>132</v>
+        <v>265</v>
       </c>
       <c r="B109" t="s">
         <v>114</v>
@@ -2847,7 +2846,7 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>133</v>
+        <v>266</v>
       </c>
       <c r="B110" t="s">
         <v>114</v>
@@ -2861,436 +2860,436 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B111" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="C111">
         <v>5.2</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="B112" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="C112">
         <v>5.4</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="B113" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="C113">
         <v>6.3</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="B114" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C114">
         <v>2.6</v>
       </c>
       <c r="D114" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="B115" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C115">
         <v>2.6</v>
       </c>
       <c r="D115" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="B116" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C116">
         <v>2.6</v>
       </c>
       <c r="D116" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="B117" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C117">
         <v>2.6</v>
       </c>
       <c r="D117" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="B118" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C118">
         <v>2.6</v>
       </c>
       <c r="D118" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="B119" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C119">
         <v>2.6</v>
       </c>
       <c r="D119" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="B120" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C120">
         <v>2.6</v>
       </c>
       <c r="D120" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="B121" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C121">
         <v>2.6</v>
       </c>
       <c r="D121" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="B122" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C122">
         <v>2.6</v>
       </c>
       <c r="D122" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="B123" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C123">
         <v>2.6</v>
       </c>
       <c r="D123" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B124" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C124">
         <v>3.5</v>
       </c>
       <c r="D124" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="B125" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C125">
         <v>3.5</v>
       </c>
       <c r="D125" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="B126" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C126">
         <v>3.5</v>
       </c>
       <c r="D126" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="B127" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C127">
         <v>3.5</v>
       </c>
       <c r="D127" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="B128" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C128">
         <v>3.7</v>
       </c>
       <c r="D128" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="B129" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C129">
         <v>4.9000000000000004</v>
       </c>
       <c r="D129" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="B130" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C130">
         <v>3.5</v>
       </c>
       <c r="D130" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="B131" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="C131">
         <v>2.9</v>
       </c>
       <c r="D131" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="B132" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="C132">
         <v>20.5</v>
       </c>
       <c r="D132" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="B133" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="C133">
         <v>20.5</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B134" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="C134">
         <v>20.5</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="B135" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="C135">
         <v>20.5</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="B136" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="C136">
         <v>2.9</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="B137" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="C137">
         <v>2.9</v>
       </c>
-      <c r="D137" s="4" t="s">
-        <v>242</v>
+      <c r="D137" s="2" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="B138" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="C138">
         <v>2.9</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="B139" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="C139">
         <v>3.3</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="B140" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="C140">
         <v>4.2</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="B141" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="C141">
         <v>6.2</v>
       </c>
       <c r="D141" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
